--- a/vse-loti/340098623/spec-340098623.xlsx
+++ b/vse-loti/340098623/spec-340098623.xlsx
@@ -16,8 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="#,##0.00&quot; ₽&quot;"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00&quot; ₽&quot;"/>
   </numFmts>
   <fonts count="4">
     <font>
@@ -82,15 +83,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -526,43 +530,62 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>ГОСТ 9941-2022 8352</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
+          <t>Труба 20х2-6000 08Х22Н6Т МКК ГОСТ 9941-81 (1392 шт.) Трубы должны быть гидроиспытаны и испытаны на раздачу, термообработанные , Соответст -т пункт 2.2 ( трубы под сварку); 2.3; 2,4; 2.7; 2.8; 2.9; 3.1 ГОСТ 9941-2022</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>20×2</t>
+        </is>
+      </c>
       <c r="D2" s="3" t="n">
-        <v>6</v>
+        <v>8352</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
           <t>м</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
+      <c r="F2" s="4" t="n">
+        <v>7.415</v>
+      </c>
+      <c r="G2" s="5" t="n">
+        <v>8112381.12</v>
+      </c>
+      <c r="H2" s="5" t="n">
+        <v>1094063.98</v>
+      </c>
+      <c r="I2" s="5" t="n">
+        <v>1312876.77</v>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
+      </c>
+      <c r="F3" s="7" t="n">
+        <v>7.415</v>
+      </c>
+      <c r="G3" s="8" t="n">
+        <v>8112381.12</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>НМЦК из обоснования:</t>
         </is>
       </c>
-      <c r="G4" s="5" t="n">
+      <c r="G4" s="8" t="n">
         <v>8112381.12</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>Источник: preview.txt</t>
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>Источник: Извещение о проведении запроса предложений 380-26-УМТО-ЭТП с ТЗ.docx</t>
         </is>
       </c>
     </row>
